--- a/20251229_new_progress/Code/paper_data_newdata/main_paper_results/MAIN_PAPER_SOURCE_INDEX.xlsx
+++ b/20251229_new_progress/Code/paper_data_newdata/main_paper_results/MAIN_PAPER_SOURCE_INDEX.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,22 +28,13 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -64,16 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,252 +425,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="77" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Folder</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Paper section</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Main source folders</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>00_methodology_and_data_audit</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Methods and data audit</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Feature_Decomposition; data_cleaning_audit; tables/table1 methodology notes</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Data cleaning, ID alignment, questionnaire decomposition, peer nomination cleaning, and feature construction.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>01_model_performance</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Model comparison</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>logistic_baseline; Ridge_lasso; GNN_baseline; tables/table3</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Compare original Logistic, decomposed Logistic, LASSO/Ridge, and GraphSAGE for W2-&gt;W2 and W2-&gt;W3.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>02_descriptive_table1_group_differences</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Descriptive Table 1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>tables/table1</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Compare high vs low psychological distress groups, including the 12 interpersonal network indicators.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>03_interpersonal_incremental_modeling</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Incremental network-feature test</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>to be generated</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Run decomposed-feature models with and without the 12 interpersonal indicators and evaluate performance/selection.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>04_feature_importance_top20</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Feature importance</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Ridge_lasso; tables/table2 outputs</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Use LASSO relative importance to identify Top 20 predictors for W2-&gt;W2 and W2-&gt;W3.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>05_category_level_interpretation</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Domain-level interpretation</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Top 20 outputs</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Group Top 20 variables into theoretical domains and plot category-level importance.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>06_interaction_analysis</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Moderation/protection tests</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>04_feature_importance_top20; current feature construction</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estimate teacher-formula interaction models with b0, b1, b2, b3, derived intercepts/slopes, and predicted probabilities for Top20 Feature x Online Activity / PIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07_</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Moderator-stratified descriptive Table 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>04_feature_importance_top20; 06_interaction_analysis feature construction</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Create Table 1 style mean(SD) comparisons for LASSO Top20 features by high/low Online Activity and Problematic Internet Use groups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>08_family_online_2x2_risk_test</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2x2 subgroup risk test</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>06_interaction_analysis; W2 cleaned data; W3 cleaned data</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Test whether lower W2 family cohesion plus high W2 online activity identifies a higher-risk subgroup for high psychological distress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09_longitudinal_change_analysis</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Longitudinal change</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>to be generated</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Test High Online Activity x SEL/resilience/bullying/digital literacy interactions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>07_longitudinal_change_analysis</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Longitudinal change</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>to be generated</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Analyze W2 predictors of W3 distress and distress transition/change groups.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>08_figures_and_manuscript_exports</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10_figures_and_manuscript_exports</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Final exports</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>all finalized outputs</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Store manuscript-ready tables, figures, and simplified exports.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>99_archive_or_supplementary</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Archive/supplement</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>older or exploratory outputs</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Store results that are not part of the main narrative.</t>
         </is>
